--- a/Reports/Sample_Product_A_Setup_Report.xlsx
+++ b/Reports/Sample_Product_A_Setup_Report.xlsx
@@ -43,7 +43,7 @@
     <x:t>Imported Date</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-09-23 03:07:52</x:t>
+    <x:t>2026-09-23 10:45:52</x:t>
   </x:si>
   <x:si>
     <x:t>Machine Name</x:t>
